--- a/640__Introducao/Pasta1.xlsx
+++ b/640__Introducao/Pasta1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12276" windowHeight="2988"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="12276" windowHeight="2988"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +163,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -246,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -669,7 +677,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
@@ -680,7 +688,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" s="6">
         <v>2</v>
@@ -691,10 +699,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -805,7 +813,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="10"/>
     </row>
@@ -820,7 +828,7 @@
         <v>37</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="10"/>
     </row>
@@ -836,12 +844,11 @@
     <hyperlink ref="D4" r:id="rId2"/>
     <hyperlink ref="D5" r:id="rId3"/>
     <hyperlink ref="D6" r:id="rId4"/>
-    <hyperlink ref="D22" r:id="rId5" display="a@email.com"/>
-    <hyperlink ref="D23" r:id="rId6" display="b@email.com"/>
-    <hyperlink ref="D24" r:id="rId7" display="c@email.com"/>
-    <hyperlink ref="D25" r:id="rId8" display="d@email.com"/>
+    <hyperlink ref="D23" r:id="rId5" display="b@email.com"/>
+    <hyperlink ref="D24" r:id="rId6" display="c@email.com"/>
+    <hyperlink ref="D25" r:id="rId7" display="d@email.com"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId8"/>
 </worksheet>
 </file>